--- a/awatifMapping/ig/cm-v3-administrative-gender.xlsx
+++ b/awatifMapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T13:19:58+00:00</t>
+    <t>2026-03-16T13:48:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
